--- a/artfynd/A 24817-2025 artfynd.xlsx
+++ b/artfynd/A 24817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103059598</v>
+        <v>69525955</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalmar län, Sm</t>
+          <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564870.1769959586</v>
+        <v>564831</v>
       </c>
       <c r="R2" t="n">
-        <v>6261728.812308698</v>
+        <v>6261635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,34 +738,19 @@
           <t>Halltorp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>8943CF7A-43BF-49A5-B156-209176E70640</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inventerare Karl Nordström</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Helén Wåhlstrand Persson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +762,21 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -798,6 +789,247 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädinventeringen i Kalmar län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102977011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kalmar län, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>564830</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6261635</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Halltorp</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>97BCA3FD-116C-477D-9C2D-5A0314A9FB52</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-03-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-03-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med trädinventering.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helén Wåhlstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103059598</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalmar län, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>564870</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6261729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Halltorp</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8943CF7A-43BF-49A5-B156-209176E70640</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-03-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-03-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventerare Karl Nordström</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
